--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/big data sheet for Deepta.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/big data sheet for Deepta.xlsx
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8.996565656565645</v>
+        <v>-37.50397575757572</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8794245288557566</v>
+        <v>0.972678421313059</v>
       </c>
     </row>
     <row r="3">
@@ -525,10 +525,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.667400000000003</v>
+        <v>-22.45138363636364</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8375324640275021</v>
+        <v>0.9541091672339933</v>
       </c>
     </row>
     <row r="4">
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>33.24565656565642</v>
+        <v>-480.6158747474745</v>
       </c>
       <c r="G4" t="n">
-        <v>0.581965319962624</v>
+        <v>0.6915787712471098</v>
       </c>
     </row>
     <row r="5">
@@ -591,10 +591,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.409063636363627</v>
+        <v>-21.81943181818183</v>
       </c>
       <c r="G5" t="n">
-        <v>0.825482825597738</v>
+        <v>0.9349201213330283</v>
       </c>
     </row>
     <row r="6">
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10.2145454545455</v>
+        <v>-372.7660646464645</v>
       </c>
       <c r="G6" t="n">
-        <v>0.384416518841273</v>
+        <v>0.8070678328649753</v>
       </c>
     </row>
     <row r="7">
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5.313627272727275</v>
+        <v>-22.10032090909091</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9465584013393388</v>
+        <v>0.9340870600912793</v>
       </c>
     </row>
     <row r="8">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>14.74020202020189</v>
+        <v>-218.0203272727272</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8795674361921604</v>
+        <v>0.8862823435872961</v>
       </c>
     </row>
     <row r="9">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.943799999999998</v>
+        <v>-23.71597454545455</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9113690927293407</v>
+        <v>0.9502264641232183</v>
       </c>
     </row>
     <row r="10">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>527.3686666666663</v>
+        <v>426.4630303030301</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6589450876539205</v>
+        <v>0.5919976104734694</v>
       </c>
     </row>
     <row r="11">
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.19991818181819</v>
+        <v>-21.29346545454547</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9647815228044454</v>
+        <v>0.9676647714649318</v>
       </c>
     </row>
     <row r="12">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10.60242424242426</v>
+        <v>-52.0103919191919</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9262433101428021</v>
+        <v>0.9972866649104942</v>
       </c>
     </row>
     <row r="13">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.960400000000009</v>
+        <v>-27.88579090909092</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8532653059956311</v>
+        <v>0.9703289169114947</v>
       </c>
     </row>
     <row r="14">
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>17.38864646464646</v>
+        <v>-65.24827474747471</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7463386569306016</v>
+        <v>0.6991634150592152</v>
       </c>
     </row>
     <row r="15">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.923945454545463</v>
+        <v>-27.09638454545455</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7757886699438762</v>
+        <v>0.9617362537755447</v>
       </c>
     </row>
     <row r="16">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>17.96371717171717</v>
+        <v>-64.36324848484844</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6418775196002673</v>
+        <v>0.7202095951091531</v>
       </c>
     </row>
     <row r="17">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5.609927272727284</v>
+        <v>-24.77479272727274</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8334431745673975</v>
+        <v>0.9481987960555942</v>
       </c>
     </row>
     <row r="18">
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>21.22658585858584</v>
+        <v>-65.88481212121208</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6662887638521571</v>
+        <v>0.7217373750896391</v>
       </c>
     </row>
     <row r="19">
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5.713918181818185</v>
+        <v>-23.75943363636365</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8056865792882439</v>
+        <v>0.9432986651362413</v>
       </c>
     </row>
     <row r="20">
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>16.62715151515152</v>
+        <v>-53.03591515151513</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5758131876951806</v>
+        <v>0.6608950413459149</v>
       </c>
     </row>
     <row r="21">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5.654490909090917</v>
+        <v>-27.25216090909092</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8913706895073455</v>
+        <v>0.9709030925219538</v>
       </c>
     </row>
     <row r="22">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10.47283636363636</v>
+        <v>-2.627070707070705</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9011014901200753</v>
+        <v>0.9681156089026531</v>
       </c>
     </row>
     <row r="23">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.138208181818184</v>
+        <v>-1.445656363636364</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6879533710360769</v>
+        <v>0.8750411210432337</v>
       </c>
     </row>
     <row r="24">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>37.01627474747474</v>
+        <v>-3.818549494949495</v>
       </c>
       <c r="G24" t="n">
-        <v>0.787100792938741</v>
+        <v>0.6531404612279088</v>
       </c>
     </row>
     <row r="25">
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5.832891818181823</v>
+        <v>-1.296960909090909</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7424844093887175</v>
+        <v>0.9294005691979321</v>
       </c>
     </row>
     <row r="26">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>41.53647272727272</v>
+        <v>-3.478989898989898</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7880056814692975</v>
+        <v>0.6667618184223156</v>
       </c>
     </row>
     <row r="27">
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>7.704281818181823</v>
+        <v>-1.224196363636364</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6039308354264715</v>
+        <v>0.7681245758723213</v>
       </c>
     </row>
     <row r="28">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>43.21177777777775</v>
+        <v>-3.693599999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>0.766539174639197</v>
+        <v>0.5655732358263068</v>
       </c>
     </row>
     <row r="29">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7.392240909090912</v>
+        <v>-1.26351090909091</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6088504440553383</v>
+        <v>0.8820606816085288</v>
       </c>
     </row>
     <row r="30">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>34.09412525252524</v>
+        <v>-2.78133737373737</v>
       </c>
       <c r="G30" t="n">
-        <v>0.640802535461336</v>
+        <v>0.7253026730219012</v>
       </c>
     </row>
     <row r="31">
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.532779090909091</v>
+        <v>-1.230491818181819</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7425656618450345</v>
+        <v>0.8813153066188024</v>
       </c>
     </row>
     <row r="32">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4.278654545454546</v>
+        <v>-2.39560808080808</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8426649141894057</v>
+        <v>0.9800054886158105</v>
       </c>
     </row>
     <row r="33">
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.586041818181819</v>
+        <v>-1.432004545454546</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5267015979224294</v>
+        <v>0.8196002333261512</v>
       </c>
     </row>
     <row r="34">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>13.88491313131313</v>
+        <v>-3.401680808080804</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7816610060826619</v>
+        <v>0.61764002997946</v>
       </c>
     </row>
     <row r="35">
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.632046363636367</v>
+        <v>-1.444497272727273</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5133026826593086</v>
+        <v>0.875471469042083</v>
       </c>
     </row>
     <row r="36">
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>15.55237171717171</v>
+        <v>-3.279365656565653</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7732944386211598</v>
+        <v>0.7108892835065735</v>
       </c>
     </row>
     <row r="37">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.002836363636367</v>
+        <v>-1.492010909090909</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5518677570875022</v>
+        <v>0.8434357291075838</v>
       </c>
     </row>
     <row r="38">
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>15.02990303030303</v>
+        <v>-3.410040404040404</v>
       </c>
       <c r="G38" t="n">
-        <v>0.748104053497075</v>
+        <v>0.6299229765323161</v>
       </c>
     </row>
     <row r="39">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.943560909090911</v>
+        <v>-1.504295454545455</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5870519508737846</v>
+        <v>0.8814651888657259</v>
       </c>
     </row>
     <row r="40">
@@ -1746,10 +1746,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>14.09021414141414</v>
+        <v>-3.667531313131308</v>
       </c>
       <c r="G40" t="n">
-        <v>0.6985548935308398</v>
+        <v>0.6149510507130794</v>
       </c>
     </row>
     <row r="41">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.214857272727273</v>
+        <v>-1.406169090909091</v>
       </c>
       <c r="G41" t="n">
-        <v>0.7568726251722585</v>
+        <v>0.8166448274152978</v>
       </c>
     </row>
     <row r="42">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.705882828282829</v>
+        <v>-2.912298989898987</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8770982476787517</v>
+        <v>0.9777740186049994</v>
       </c>
     </row>
     <row r="43">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.626778181818182</v>
+        <v>-1.54781090909091</v>
       </c>
       <c r="G43" t="n">
-        <v>0.6852763757187053</v>
+        <v>0.8782574892678259</v>
       </c>
     </row>
     <row r="44">
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>7.469078787878777</v>
+        <v>-3.394460606060606</v>
       </c>
       <c r="G44" t="n">
-        <v>0.793628743687723</v>
+        <v>0.6414032323397187</v>
       </c>
     </row>
     <row r="45">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.710478181818181</v>
+        <v>-1.440235454545456</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7897022683415071</v>
+        <v>0.868128674072792</v>
       </c>
     </row>
     <row r="46">
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>7.551022222222224</v>
+        <v>-3.393624242424238</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8058326994322833</v>
+        <v>0.6881149926168879</v>
       </c>
     </row>
     <row r="47">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.737322727272728</v>
+        <v>-1.509303636363637</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8258715047280594</v>
+        <v>0.8988091838328862</v>
       </c>
     </row>
     <row r="48">
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>7.367082828282826</v>
+        <v>-3.497163636363636</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8304752277065029</v>
+        <v>0.6347553182055817</v>
       </c>
     </row>
     <row r="49">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.178786363636364</v>
+        <v>-1.470068181818183</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8200350867490043</v>
+        <v>0.8682293578306235</v>
       </c>
     </row>
     <row r="50">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>7.435284848484847</v>
+        <v>-3.050638383838383</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8114529575389947</v>
+        <v>0.6628863873004975</v>
       </c>
     </row>
     <row r="51">
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.454750000000001</v>
+        <v>-1.414528181818182</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8488163770613285</v>
+        <v>0.8671005775173937</v>
       </c>
     </row>
     <row r="52">
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>5.309705050505054</v>
+        <v>-2.871951515151512</v>
       </c>
       <c r="G52" t="n">
-        <v>0.8834568304463893</v>
+        <v>0.978453567199069</v>
       </c>
     </row>
     <row r="53">
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.865154545454546</v>
+        <v>-1.533323636363639</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8190060548652909</v>
+        <v>0.9699908227138575</v>
       </c>
     </row>
     <row r="54">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>17.24204444444443</v>
+        <v>-4.149640404040402</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8163462223002156</v>
+        <v>0.6449792008591217</v>
       </c>
     </row>
     <row r="55">
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>4.391087272727273</v>
+        <v>-1.744940000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6672965072847483</v>
+        <v>0.853347094252574</v>
       </c>
     </row>
     <row r="56">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>17.98509494949494</v>
+        <v>-3.900658585858582</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8088148323305492</v>
+        <v>0.6710588704656015</v>
       </c>
     </row>
     <row r="57">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>5.369228181818183</v>
+        <v>-1.735296363636365</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6206982333860298</v>
+        <v>0.8453735789915091</v>
       </c>
     </row>
     <row r="58">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>20.47941818181817</v>
+        <v>-3.941644444444439</v>
       </c>
       <c r="G58" t="n">
-        <v>0.7596590707213231</v>
+        <v>0.6437900758626196</v>
       </c>
     </row>
     <row r="59">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3.455628181818182</v>
+        <v>-1.659978181818183</v>
       </c>
       <c r="G59" t="n">
-        <v>0.6739983059229322</v>
+        <v>0.8331289597061327</v>
       </c>
     </row>
     <row r="60">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>14.47309494949494</v>
+        <v>-2.959418181818185</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6715854209251828</v>
+        <v>0.8490674881485568</v>
       </c>
     </row>
     <row r="61">
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.194604545454548</v>
+        <v>-1.550083636363637</v>
       </c>
       <c r="G61" t="n">
-        <v>0.7148283333963688</v>
+        <v>0.8615320803414876</v>
       </c>
     </row>
     <row r="62">
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>6.092808080808069</v>
+        <v>-20.2976</v>
       </c>
       <c r="G62" t="n">
-        <v>0.8402370820929643</v>
+        <v>0.9230854227094574</v>
       </c>
     </row>
     <row r="63">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3.382945454545454</v>
+        <v>-14.37586545454546</v>
       </c>
       <c r="G63" t="n">
-        <v>0.7871509720150481</v>
+        <v>0.9652062299755559</v>
       </c>
     </row>
     <row r="64">
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>14.08420202020202</v>
+        <v>-30.9517818181818</v>
       </c>
       <c r="G64" t="n">
-        <v>0.6794702126257925</v>
+        <v>0.8383669640040059</v>
       </c>
     </row>
     <row r="65">
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>4.088163636363642</v>
+        <v>-13.68887636363637</v>
       </c>
       <c r="G65" t="n">
-        <v>0.7900928233985015</v>
+        <v>0.9624453946559356</v>
       </c>
     </row>
     <row r="66">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>16.3182222222222</v>
+        <v>-38.61042020202017</v>
       </c>
       <c r="G66" t="n">
-        <v>0.6300277333930762</v>
+        <v>0.678453867167222</v>
       </c>
     </row>
     <row r="67">
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>4.899072727272724</v>
+        <v>-14.37158454545455</v>
       </c>
       <c r="G67" t="n">
-        <v>0.7395676176309718</v>
+        <v>0.9792648261705701</v>
       </c>
     </row>
     <row r="68">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>16.65507070707069</v>
+        <v>-34.70054141414138</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6182037104381355</v>
+        <v>0.7476839580654808</v>
       </c>
     </row>
     <row r="69">
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>4.192209090909095</v>
+        <v>-13.74915090909091</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8399937214718683</v>
+        <v>0.9683776156934237</v>
       </c>
     </row>
     <row r="70">
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>8.901252525252515</v>
+        <v>-20.91579797979797</v>
       </c>
       <c r="G70" t="n">
-        <v>0.711287204355235</v>
+        <v>0.8538098851833423</v>
       </c>
     </row>
     <row r="71">
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3.586499999999999</v>
+        <v>-14.37907181818182</v>
       </c>
       <c r="G71" t="n">
-        <v>0.955810865805426</v>
+        <v>0.9633287099674115</v>
       </c>
     </row>
     <row r="72">
@@ -2802,10 +2802,10 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>4.267959595959597</v>
+        <v>-19.64961616161616</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9183431912954843</v>
+        <v>0.9832208591417874</v>
       </c>
     </row>
     <row r="73">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3.099590909090912</v>
+        <v>-14.10911545454546</v>
       </c>
       <c r="G73" t="n">
-        <v>0.8868791000225879</v>
+        <v>0.9505386780946128</v>
       </c>
     </row>
     <row r="74">
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>11.98630303030303</v>
+        <v>-32.82238383838381</v>
       </c>
       <c r="G74" t="n">
-        <v>0.6949945721184827</v>
+        <v>0.7444171875862312</v>
       </c>
     </row>
     <row r="75">
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>4.848390909090909</v>
+        <v>-14.85204090909092</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8099343197311535</v>
+        <v>0.9488099350772754</v>
       </c>
     </row>
     <row r="76">
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>13.99349494949496</v>
+        <v>-31.38759595959594</v>
       </c>
       <c r="G76" t="n">
-        <v>0.7347222496279326</v>
+        <v>0.7571051927997772</v>
       </c>
     </row>
     <row r="77">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>4.716490909090905</v>
+        <v>-15.17563000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>0.812094956991771</v>
+        <v>0.9569531134723402</v>
       </c>
     </row>
     <row r="78">
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>14.02731313131312</v>
+        <v>-32.2495636363636</v>
       </c>
       <c r="G78" t="n">
-        <v>0.6516756130649342</v>
+        <v>0.7591992381083721</v>
       </c>
     </row>
     <row r="79">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3.817763636363644</v>
+        <v>-13.50198727272728</v>
       </c>
       <c r="G79" t="n">
-        <v>0.7931221686637031</v>
+        <v>0.9380464480884607</v>
       </c>
     </row>
     <row r="80">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>12.99527272727271</v>
+        <v>-26.40959191919191</v>
       </c>
       <c r="G80" t="n">
-        <v>0.6164979766407166</v>
+        <v>0.7352351672603725</v>
       </c>
     </row>
     <row r="81">
@@ -3099,10 +3099,10 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3.291018181818184</v>
+        <v>-14.28613181818182</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9604791192845267</v>
+        <v>0.9471377950487018</v>
       </c>
     </row>
     <row r="82">
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3.962424242424246</v>
+        <v>-21.02683636363635</v>
       </c>
       <c r="G82" t="n">
-        <v>0.8830491762315342</v>
+        <v>0.9433572427992476</v>
       </c>
     </row>
     <row r="83">
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2.866418181818187</v>
+        <v>-12.68963272727273</v>
       </c>
       <c r="G83" t="n">
-        <v>0.8695928958221073</v>
+        <v>0.9704802138758603</v>
       </c>
     </row>
     <row r="84">
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>8.573333333333345</v>
+        <v>-20.60633535353535</v>
       </c>
       <c r="G84" t="n">
-        <v>0.7999202409490579</v>
+        <v>0.8387372855793448</v>
       </c>
     </row>
     <row r="85">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3.061081818181819</v>
+        <v>-11.61985181818182</v>
       </c>
       <c r="G85" t="n">
-        <v>0.802532024373813</v>
+        <v>0.9569999749878133</v>
       </c>
     </row>
     <row r="86">
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>6.473737373737359</v>
+        <v>-15.43025454545455</v>
       </c>
       <c r="G86" t="n">
-        <v>0.8344358310449094</v>
+        <v>0.98809099365428</v>
       </c>
     </row>
     <row r="87">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2.661963636363638</v>
+        <v>-11.03773818181818</v>
       </c>
       <c r="G87" t="n">
-        <v>0.8407838787945897</v>
+        <v>0.9780880240470782</v>
       </c>
     </row>
     <row r="88">
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>9.173292929292922</v>
+        <v>-23.43124444444444</v>
       </c>
       <c r="G88" t="n">
-        <v>0.7538672745885577</v>
+        <v>0.858736919093397</v>
       </c>
     </row>
     <row r="89">
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2.794672727272728</v>
+        <v>-9.593325454545459</v>
       </c>
       <c r="G89" t="n">
-        <v>0.8456022861121422</v>
+        <v>0.9706949790521935</v>
       </c>
     </row>
     <row r="90">
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>5.637212121212102</v>
+        <v>-15.06747474747475</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6105001339665941</v>
+        <v>0.8227021084733903</v>
       </c>
     </row>
     <row r="91">
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2.867218181818179</v>
+        <v>-12.24536727272728</v>
       </c>
       <c r="G91" t="n">
-        <v>0.9639563000355189</v>
+        <v>0.9397294326520751</v>
       </c>
     </row>
     <row r="92">
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>8.923313131313124</v>
+        <v>-22.81343838383837</v>
       </c>
       <c r="G92" t="n">
-        <v>0.8944764625152581</v>
+        <v>0.962803103913451</v>
       </c>
     </row>
     <row r="93">
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3.10258181818182</v>
+        <v>-11.92744000000001</v>
       </c>
       <c r="G93" t="n">
-        <v>0.9047165911352977</v>
+        <v>0.9777856180689309</v>
       </c>
     </row>
     <row r="94">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>15.89684848484848</v>
+        <v>-33.15644848484846</v>
       </c>
       <c r="G94" t="n">
-        <v>0.6911105561770223</v>
+        <v>0.7159676270216557</v>
       </c>
     </row>
     <row r="95">
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>5.888472727272723</v>
+        <v>-14.70044000000001</v>
       </c>
       <c r="G95" t="n">
-        <v>0.7765347623485929</v>
+        <v>0.9561074818459224</v>
       </c>
     </row>
     <row r="96">
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>17.13313131313129</v>
+        <v>-33.39609696969696</v>
       </c>
       <c r="G96" t="n">
-        <v>0.6406150818375295</v>
+        <v>0.7153461403970505</v>
       </c>
     </row>
     <row r="97">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>4.656045454545455</v>
+        <v>-12.52096909090909</v>
       </c>
       <c r="G97" t="n">
-        <v>0.7075417273562996</v>
+        <v>0.9454446078264521</v>
       </c>
     </row>
     <row r="98">
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>19.51939393939391</v>
+        <v>-31.05272323232322</v>
       </c>
       <c r="G98" t="n">
-        <v>0.6602846146307574</v>
+        <v>0.7338218151830571</v>
       </c>
     </row>
     <row r="99">
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>4.416436363636365</v>
+        <v>-12.27974363636364</v>
       </c>
       <c r="G99" t="n">
-        <v>0.713714052237765</v>
+        <v>0.9327377433152492</v>
       </c>
     </row>
     <row r="100">
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>13.79531313131312</v>
+        <v>-22.58870303030302</v>
       </c>
       <c r="G100" t="n">
-        <v>0.6495530580074684</v>
+        <v>0.8227032303863091</v>
       </c>
     </row>
     <row r="101">
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2.562818181818187</v>
+        <v>-12.72193727272727</v>
       </c>
       <c r="G101" t="n">
-        <v>0.915964346805708</v>
+        <v>0.9311485216396203</v>
       </c>
     </row>
     <row r="102">
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>9.245696969696994</v>
+        <v>-20.14672727272727</v>
       </c>
       <c r="G102" t="n">
-        <v>0.7393831279410689</v>
+        <v>0.9935557014719759</v>
       </c>
     </row>
     <row r="103">
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>5.549500000000004</v>
+        <v>-17.36455000000001</v>
       </c>
       <c r="G103" t="n">
-        <v>0.8357990490648253</v>
+        <v>0.9778630173741161</v>
       </c>
     </row>
     <row r="104">
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>16.65979797979796</v>
+        <v>-31.75097777777777</v>
       </c>
       <c r="G104" t="n">
-        <v>0.6118737111646202</v>
+        <v>0.7999508110127698</v>
       </c>
     </row>
     <row r="105">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>6.308400000000008</v>
+        <v>-17.64614090909092</v>
       </c>
       <c r="G105" t="n">
-        <v>0.7558396939741151</v>
+        <v>0.9767080238395333</v>
       </c>
     </row>
     <row r="106">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>18.66153535353534</v>
+        <v>-38.18604848484847</v>
       </c>
       <c r="G106" t="n">
-        <v>0.5160664894966738</v>
+        <v>0.6910786524036268</v>
       </c>
     </row>
     <row r="107">
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>5.928845454545454</v>
+        <v>-17.16017090909092</v>
       </c>
       <c r="G107" t="n">
-        <v>0.808818475341107</v>
+        <v>0.9635789506905461</v>
       </c>
     </row>
     <row r="108">
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>18.48557575757577</v>
+        <v>-32.88502626262624</v>
       </c>
       <c r="G108" t="n">
-        <v>0.5840511834203159</v>
+        <v>0.7448607672094312</v>
       </c>
     </row>
     <row r="109">
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>5.635163636363643</v>
+        <v>-18.17090181818183</v>
       </c>
       <c r="G109" t="n">
-        <v>0.841420311225941</v>
+        <v>0.9792219810319839</v>
       </c>
     </row>
     <row r="110">
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>18.63006060606058</v>
+        <v>-28.05983030303029</v>
       </c>
       <c r="G110" t="n">
-        <v>0.5669835260635754</v>
+        <v>0.787135982337311</v>
       </c>
     </row>
     <row r="111">
@@ -4089,10 +4089,10 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>4.353100000000006</v>
+        <v>-17.35326272727273</v>
       </c>
       <c r="G111" t="n">
-        <v>0.9263656936232946</v>
+        <v>0.9613737969802968</v>
       </c>
     </row>
     <row r="112">
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>11.17244444444445</v>
+        <v>-29.81060202020199</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8839730504716621</v>
+        <v>0.943734271886474</v>
       </c>
     </row>
     <row r="113">
@@ -4155,10 +4155,10 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3.36587272727272</v>
+        <v>-14.58598545454546</v>
       </c>
       <c r="G113" t="n">
-        <v>0.8948250889810463</v>
+        <v>0.9888062570007098</v>
       </c>
     </row>
     <row r="114">
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>21.86028282828282</v>
+        <v>-38.05063838383836</v>
       </c>
       <c r="G114" t="n">
-        <v>0.6720121420972444</v>
+        <v>0.7297740402898987</v>
       </c>
     </row>
     <row r="115">
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>46.1638090909091</v>
+        <v>-16.53843363636365</v>
       </c>
       <c r="G115" t="n">
-        <v>0.925478077697259</v>
+        <v>0.9581042671611582</v>
       </c>
     </row>
     <row r="116">
@@ -4254,10 +4254,10 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>81.10674747474742</v>
+        <v>-44.22435151515148</v>
       </c>
       <c r="G116" t="n">
-        <v>0.6595638192778606</v>
+        <v>0.6531711941530034</v>
       </c>
     </row>
     <row r="117">
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>8.62427272727273</v>
+        <v>-14.71286727272728</v>
       </c>
       <c r="G117" t="n">
-        <v>0.9648575246732884</v>
+        <v>0.9753233582905136</v>
       </c>
     </row>
     <row r="118">
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>82.07599999999996</v>
+        <v>-42.45242828282826</v>
       </c>
       <c r="G118" t="n">
-        <v>0.6179157387107133</v>
+        <v>0.7348249716838045</v>
       </c>
     </row>
     <row r="119">
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>9.068536363636367</v>
+        <v>-16.39140545454546</v>
       </c>
       <c r="G119" t="n">
-        <v>0.5177095814858492</v>
+        <v>0.9572251252199594</v>
       </c>
     </row>
     <row r="120">
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>39.54573737373736</v>
+        <v>-35.50595959595958</v>
       </c>
       <c r="G120" t="n">
-        <v>0.4770973021572507</v>
+        <v>0.7255201953769504</v>
       </c>
     </row>
     <row r="121">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>3.790827272727272</v>
+        <v>-14.39538727272728</v>
       </c>
       <c r="G121" t="n">
-        <v>0.7888510319233842</v>
+        <v>0.9261395244309798</v>
       </c>
     </row>
     <row r="122">
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>9.610909090909113</v>
+        <v>-25.15858585858584</v>
       </c>
       <c r="G122" t="n">
-        <v>0.7971722938830053</v>
+        <v>0.9231650795413908</v>
       </c>
     </row>
     <row r="123">
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>3.832499999999994</v>
+        <v>-14.46969636363637</v>
       </c>
       <c r="G123" t="n">
-        <v>0.9535049939705589</v>
+        <v>0.9234484257294281</v>
       </c>
     </row>
     <row r="124">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>19.03640404040401</v>
+        <v>-38.81505858585857</v>
       </c>
       <c r="G124" t="n">
-        <v>0.6967737868059241</v>
+        <v>0.7540547875288537</v>
       </c>
     </row>
     <row r="125">
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>3.87191818181818</v>
+        <v>-14.46864363636365</v>
       </c>
       <c r="G125" t="n">
-        <v>0.805373395462612</v>
+        <v>0.9312946029936489</v>
       </c>
     </row>
     <row r="126">
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>15.9257777777778</v>
+        <v>-37.8250505050505</v>
       </c>
       <c r="G126" t="n">
-        <v>0.6322251502040663</v>
+        <v>0.744311247986984</v>
       </c>
     </row>
     <row r="127">
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>3.672663636363629</v>
+        <v>-13.63424636363637</v>
       </c>
       <c r="G127" t="n">
-        <v>0.8330245313731184</v>
+        <v>0.9179471021259278</v>
       </c>
     </row>
     <row r="128">
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>18.49466666666666</v>
+        <v>-34.98888080808079</v>
       </c>
       <c r="G128" t="n">
-        <v>0.6443430694169384</v>
+        <v>0.7300383735864906</v>
       </c>
     </row>
     <row r="129">
@@ -4683,10 +4683,10 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3.844718181818175</v>
+        <v>-13.25548818181819</v>
       </c>
       <c r="G129" t="n">
-        <v>0.9380330040131933</v>
+        <v>0.9391155014993492</v>
       </c>
     </row>
     <row r="130">
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>14.88480808080807</v>
+        <v>-32.42654545454544</v>
       </c>
       <c r="G130" t="n">
-        <v>0.5958523047765671</v>
+        <v>0.6989966219138019</v>
       </c>
     </row>
     <row r="131">
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3.622727272727279</v>
+        <v>-12.95824818181818</v>
       </c>
       <c r="G131" t="n">
-        <v>0.9448709497940507</v>
+        <v>0.9293762497199078</v>
       </c>
     </row>
     <row r="132">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>1.636585858585864</v>
+        <v>-1.951559595959596</v>
       </c>
       <c r="G132" t="n">
-        <v>0.9449212763012935</v>
+        <v>0.9782771549443503</v>
       </c>
     </row>
     <row r="133">
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>4.936076363636364</v>
+        <v>-2.351034545454547</v>
       </c>
       <c r="G133" t="n">
-        <v>0.6599442098391999</v>
+        <v>0.9521090100184716</v>
       </c>
     </row>
     <row r="134">
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>41.29028282828281</v>
+        <v>-5.423684848484846</v>
       </c>
       <c r="G134" t="n">
-        <v>0.7822942856746119</v>
+        <v>0.731703746251001</v>
       </c>
     </row>
     <row r="135">
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>7.497208181818182</v>
+        <v>-2.401213636363639</v>
       </c>
       <c r="G135" t="n">
-        <v>0.7098423384291395</v>
+        <v>0.966204624175277</v>
       </c>
     </row>
     <row r="136">
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>49.37460202020199</v>
+        <v>-5.736674747474741</v>
       </c>
       <c r="G136" t="n">
-        <v>0.7646805330596192</v>
+        <v>0.7746416768264204</v>
       </c>
     </row>
     <row r="137">
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>11.24265272727273</v>
+        <v>-2.2761</v>
       </c>
       <c r="G137" t="n">
-        <v>0.5143838463934833</v>
+        <v>0.9516652491122526</v>
       </c>
     </row>
     <row r="138">
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>37.95807676767674</v>
+        <v>-4.287098989898988</v>
       </c>
       <c r="G138" t="n">
-        <v>0.6854307478334757</v>
+        <v>0.958069385021266</v>
       </c>
     </row>
     <row r="139">
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>3.513955454545457</v>
+        <v>-2.114858181818183</v>
       </c>
       <c r="G139" t="n">
-        <v>0.8511931734485846</v>
+        <v>0.9660183803570844</v>
       </c>
     </row>
     <row r="140">
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>29.45349898989897</v>
+        <v>-3.194727272727271</v>
       </c>
       <c r="G140" t="n">
-        <v>0.6089413142632454</v>
+        <v>0.9778176132871009</v>
       </c>
     </row>
     <row r="141">
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>3.249001818181818</v>
+        <v>-2.343209090909092</v>
       </c>
       <c r="G141" t="n">
-        <v>0.8905883417508428</v>
+        <v>0.9572780423271385</v>
       </c>
     </row>
     <row r="142">
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>13.46772929292927</v>
+        <v>-3.183272727272729</v>
       </c>
       <c r="G142" t="n">
-        <v>0.913083258471372</v>
+        <v>0.9508711618626396</v>
       </c>
     </row>
     <row r="143">
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>6.838948181818187</v>
+        <v>-1.959455454545456</v>
       </c>
       <c r="G143" t="n">
-        <v>0.6551801986080144</v>
+        <v>0.8733462370582002</v>
       </c>
     </row>
     <row r="144">
@@ -5178,10 +5178,10 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>38.26069898989897</v>
+        <v>-3.693313131313132</v>
       </c>
       <c r="G144" t="n">
-        <v>0.7855633573904122</v>
+        <v>0.7536972836859989</v>
       </c>
     </row>
     <row r="145">
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>8.269902727272733</v>
+        <v>-1.795273636363636</v>
       </c>
       <c r="G145" t="n">
-        <v>0.6549610758213005</v>
+        <v>0.8429976907679186</v>
       </c>
     </row>
     <row r="146">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>42.42605656565654</v>
+        <v>-4.43500202020202</v>
       </c>
       <c r="G146" t="n">
-        <v>0.8207969117086107</v>
+        <v>0.6094433962780509</v>
       </c>
     </row>
     <row r="147">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>7.767668181818183</v>
+        <v>-1.633338181818182</v>
       </c>
       <c r="G147" t="n">
-        <v>0.6787512546895247</v>
+        <v>0.8477256784376997</v>
       </c>
     </row>
     <row r="148">
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>47.86450505050503</v>
+        <v>-4.401381818181816</v>
       </c>
       <c r="G148" t="n">
-        <v>0.8290864796231523</v>
+        <v>0.657555920613198</v>
       </c>
     </row>
     <row r="149">
@@ -5343,10 +5343,10 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>7.640758181818188</v>
+        <v>-1.805564545454545</v>
       </c>
       <c r="G149" t="n">
-        <v>0.6472345636951495</v>
+        <v>0.8655380795352772</v>
       </c>
     </row>
     <row r="150">
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>41.097301010101</v>
+        <v>-3.719204040404035</v>
       </c>
       <c r="G150" t="n">
-        <v>0.7227829054996627</v>
+        <v>0.6456107454190406</v>
       </c>
     </row>
     <row r="151">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>3.107271818181819</v>
+        <v>-1.668280000000001</v>
       </c>
       <c r="G151" t="n">
-        <v>0.8514692658990645</v>
+        <v>0.8419329899845751</v>
       </c>
     </row>
     <row r="152">
@@ -5442,10 +5442,10 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>3.297911111111102</v>
+        <v>-2.095890909090908</v>
       </c>
       <c r="G152" t="n">
-        <v>0.798575137312497</v>
+        <v>0.9021853325144134</v>
       </c>
     </row>
     <row r="153">
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2.671588181818181</v>
+        <v>-1.560857272727273</v>
       </c>
       <c r="G153" t="n">
-        <v>0.5070636211079707</v>
+        <v>0.8291456044460226</v>
       </c>
     </row>
     <row r="154">
@@ -5508,10 +5508,10 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>13.31492525252524</v>
+        <v>-4.502032323232323</v>
       </c>
       <c r="G154" t="n">
-        <v>0.7675309092960121</v>
+        <v>0.7261556997127445</v>
       </c>
     </row>
     <row r="155">
@@ -5541,10 +5541,10 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2.98794909090909</v>
+        <v>-1.287809090909093</v>
       </c>
       <c r="G155" t="n">
-        <v>0.6909028113305</v>
+        <v>0.77442695831896</v>
       </c>
     </row>
     <row r="156">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>18.51094545454544</v>
+        <v>-5.506484848484837</v>
       </c>
       <c r="G156" t="n">
-        <v>0.7311309282737299</v>
+        <v>0.6574405553933369</v>
       </c>
     </row>
     <row r="157">
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>4.117413636363636</v>
+        <v>-1.401520000000001</v>
       </c>
       <c r="G157" t="n">
-        <v>0.6181540543101616</v>
+        <v>0.8050342081215498</v>
       </c>
     </row>
     <row r="158">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>3.577685454545457</v>
+        <v>-1.401719090909091</v>
       </c>
       <c r="G158" t="n">
-        <v>0.6647683774492024</v>
+        <v>0.8583178177812452</v>
       </c>
     </row>
     <row r="159">
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>14.66879999999998</v>
+        <v>-4.788997979797975</v>
       </c>
       <c r="G159" t="n">
-        <v>0.7051014254959727</v>
+        <v>0.6677074262589666</v>
       </c>
     </row>
     <row r="160">
@@ -5706,10 +5706,10 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1.999380909090909</v>
+        <v>-1.428286363636364</v>
       </c>
       <c r="G160" t="n">
-        <v>0.7617101505901525</v>
+        <v>0.8487318567088665</v>
       </c>
     </row>
     <row r="161">
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>14.16581818181819</v>
+        <v>-23.32996363636363</v>
       </c>
       <c r="G161" t="n">
-        <v>0.763002743738123</v>
+        <v>0.8985687305599526</v>
       </c>
     </row>
     <row r="162">
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>5.903609090909098</v>
+        <v>-14.76471727272728</v>
       </c>
       <c r="G162" t="n">
-        <v>0.8243103854478718</v>
+        <v>0.9651024661503714</v>
       </c>
     </row>
     <row r="163">
@@ -5805,10 +5805,10 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>34.29470707070706</v>
+        <v>-34.45000404040402</v>
       </c>
       <c r="G163" t="n">
-        <v>0.7080100286503149</v>
+        <v>0.7990556446133571</v>
       </c>
     </row>
     <row r="164">
@@ -5838,10 +5838,10 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>6.844954545454552</v>
+        <v>-12.09335636363637</v>
       </c>
       <c r="G164" t="n">
-        <v>0.6394831083674759</v>
+        <v>0.9080248586137049</v>
       </c>
     </row>
     <row r="165">
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>39.71377777777774</v>
+        <v>-31.01564848484847</v>
       </c>
       <c r="G165" t="n">
-        <v>0.6797611514811284</v>
+        <v>0.81921800839095</v>
       </c>
     </row>
     <row r="166">
@@ -5904,10 +5904,10 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>7.459181818181831</v>
+        <v>-13.68629454545455</v>
       </c>
       <c r="G166" t="n">
-        <v>0.5416812414892261</v>
+        <v>0.9427066837553768</v>
       </c>
     </row>
     <row r="167">
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>42.31438383838382</v>
+        <v>-24.83969696969696</v>
       </c>
       <c r="G167" t="n">
-        <v>0.5798784523818054</v>
+        <v>0.8839101448579998</v>
       </c>
     </row>
     <row r="168">
@@ -5970,10 +5970,10 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>9.831545454545463</v>
+        <v>-13.19498090909091</v>
       </c>
       <c r="G168" t="n">
-        <v>0.4039836005109739</v>
+        <v>0.9435071418746409</v>
       </c>
     </row>
     <row r="169">
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>27.26985858585859</v>
+        <v>-26.21611717171717</v>
       </c>
       <c r="G169" t="n">
-        <v>0.5027549580065811</v>
+        <v>0.7327839232957681</v>
       </c>
     </row>
     <row r="170">
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>4.155036363636365</v>
+        <v>-12.71760363636364</v>
       </c>
       <c r="G170" t="n">
-        <v>0.9067662266069856</v>
+        <v>0.9284853667834136</v>
       </c>
     </row>
     <row r="171">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>16.26202020202018</v>
+        <v>-21.27137373737373</v>
       </c>
       <c r="G171" t="n">
-        <v>0.7874519216318721</v>
+        <v>0.928226100466917</v>
       </c>
     </row>
     <row r="172">
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>5.534990909090914</v>
+        <v>-14.48414727272728</v>
       </c>
       <c r="G172" t="n">
-        <v>0.7591496354901923</v>
+        <v>0.969597779567826</v>
       </c>
     </row>
     <row r="173">
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>28.55418181818182</v>
+        <v>-32.26585454545454</v>
       </c>
       <c r="G173" t="n">
-        <v>0.7485813279839573</v>
+        <v>0.7995204827570257</v>
       </c>
     </row>
     <row r="174">
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>7.17917272727273</v>
+        <v>-14.93525818181818</v>
       </c>
       <c r="G174" t="n">
-        <v>0.7074988986207846</v>
+        <v>0.9626277481591767</v>
       </c>
     </row>
     <row r="175">
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>29.5030707070707</v>
+        <v>-28.15943434343433</v>
       </c>
       <c r="G175" t="n">
-        <v>0.7578546248640088</v>
+        <v>0.8081294222196648</v>
       </c>
     </row>
     <row r="176">
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>7.031418181818182</v>
+        <v>-14.07513636363637</v>
       </c>
       <c r="G176" t="n">
-        <v>0.6650603680360521</v>
+        <v>0.9683995762166865</v>
       </c>
     </row>
     <row r="177">
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>32.0369696969697</v>
+        <v>-30.42495353535352</v>
       </c>
       <c r="G177" t="n">
-        <v>0.7247999267581471</v>
+        <v>0.8017055220604709</v>
       </c>
     </row>
     <row r="178">
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>7.125709090909089</v>
+        <v>-13.89489181818182</v>
       </c>
       <c r="G178" t="n">
-        <v>0.7478791555855622</v>
+        <v>0.9800796390268661</v>
       </c>
     </row>
     <row r="179">
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>26.56076767676766</v>
+        <v>-28.3792121212121</v>
       </c>
       <c r="G179" t="n">
-        <v>0.6168815013537058</v>
+        <v>0.7942316264562062</v>
       </c>
     </row>
     <row r="180">
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>4.37090909090909</v>
+        <v>-14.36645090909091</v>
       </c>
       <c r="G180" t="n">
-        <v>0.9153260808854843</v>
+        <v>0.9673500237288759</v>
       </c>
     </row>
     <row r="181">
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>26.46297777777776</v>
+        <v>-1.952799999999998</v>
       </c>
       <c r="G181" t="n">
-        <v>0.8958444136634101</v>
+        <v>0.9672041074016704</v>
       </c>
     </row>
     <row r="182">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>6.464507272727276</v>
+        <v>-1.287613636363637</v>
       </c>
       <c r="G182" t="n">
-        <v>0.8557570502162608</v>
+        <v>0.826392390775974</v>
       </c>
     </row>
     <row r="183">
@@ -6465,10 +6465,10 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>22.51890101010101</v>
+        <v>-3.471438383838385</v>
       </c>
       <c r="G183" t="n">
-        <v>0.89800092540965</v>
+        <v>0.6108458168580717</v>
       </c>
     </row>
     <row r="184">
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>8.275486363636368</v>
+        <v>-1.24781090909091</v>
       </c>
       <c r="G184" t="n">
-        <v>0.7550903818329682</v>
+        <v>0.8700010424786834</v>
       </c>
     </row>
     <row r="185">
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>34.17668282828281</v>
+        <v>-3.990282828282824</v>
       </c>
       <c r="G185" t="n">
-        <v>0.860468693354978</v>
+        <v>0.6473732552598912</v>
       </c>
     </row>
     <row r="186">
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>8.740100000000004</v>
+        <v>-1.196711818181819</v>
       </c>
       <c r="G186" t="n">
-        <v>0.622773087769549</v>
+        <v>0.8280693698828427</v>
       </c>
     </row>
     <row r="187">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>46.72072323232322</v>
+        <v>-3.045874747474749</v>
       </c>
       <c r="G187" t="n">
-        <v>0.7846250418509322</v>
+        <v>0.7101909152496924</v>
       </c>
     </row>
     <row r="188">
@@ -6630,10 +6630,10 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>5.999124545454547</v>
+        <v>-1.215722727272728</v>
       </c>
       <c r="G188" t="n">
-        <v>0.6667344133180643</v>
+        <v>0.8565864725263191</v>
       </c>
     </row>
     <row r="189">
@@ -6663,10 +6663,10 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>36.93319999999998</v>
+        <v>-3.225123232323232</v>
       </c>
       <c r="G189" t="n">
-        <v>0.7527629220618762</v>
+        <v>0.6379910571848444</v>
       </c>
     </row>
     <row r="190">
@@ -6696,10 +6696,10 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>4.400414545454549</v>
+        <v>-1.185210909090911</v>
       </c>
       <c r="G190" t="n">
-        <v>0.7394599306348382</v>
+        <v>0.8817243253500848</v>
       </c>
     </row>
     <row r="191">
@@ -6729,10 +6729,10 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>6.091870707070706</v>
+        <v>-5.359640404040404</v>
       </c>
       <c r="G191" t="n">
-        <v>0.8200141343739944</v>
+        <v>0.9901892904203173</v>
       </c>
     </row>
     <row r="192">
@@ -6762,10 +6762,10 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1.015920909090911</v>
+        <v>-2.565935454545453</v>
       </c>
       <c r="G192" t="n">
-        <v>0.6441311919068831</v>
+        <v>0.9671730957505513</v>
       </c>
     </row>
     <row r="193">
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>12.54313535353535</v>
+        <v>-9.701967676767678</v>
       </c>
       <c r="G193" t="n">
-        <v>0.671720487484802</v>
+        <v>0.8151246477845386</v>
       </c>
     </row>
     <row r="194">
@@ -6828,10 +6828,10 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>2.079403636363638</v>
+        <v>-2.640709090909091</v>
       </c>
       <c r="G194" t="n">
-        <v>0.6657026981799373</v>
+        <v>0.9319736092746843</v>
       </c>
     </row>
     <row r="195">
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>18.32758787878786</v>
+        <v>-9.347862626262627</v>
       </c>
       <c r="G195" t="n">
-        <v>0.6676236858458666</v>
+        <v>0.7484432308000386</v>
       </c>
     </row>
     <row r="196">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>2.992268181818182</v>
+        <v>-2.798910000000003</v>
       </c>
       <c r="G196" t="n">
-        <v>0.6195461860252797</v>
+        <v>0.9371534030276948</v>
       </c>
     </row>
     <row r="197">
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>16.99678787878787</v>
+        <v>-7.848521212121212</v>
       </c>
       <c r="G197" t="n">
-        <v>0.6759030250044606</v>
+        <v>0.8008755057278227</v>
       </c>
     </row>
     <row r="198">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2.249671818181818</v>
+        <v>-2.604157272727273</v>
       </c>
       <c r="G198" t="n">
-        <v>0.7398650631315759</v>
+        <v>0.9445467725896241</v>
       </c>
     </row>
     <row r="199">
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>11.73439191919191</v>
+        <v>-4.741486868686867</v>
       </c>
       <c r="G199" t="n">
-        <v>0.6662670683308962</v>
+        <v>0.9597950951762305</v>
       </c>
     </row>
     <row r="200">
@@ -7026,10 +7026,10 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1.213353636363637</v>
+        <v>-2.888335454545456</v>
       </c>
       <c r="G200" t="n">
-        <v>0.9404117707538031</v>
+        <v>0.9460707702910727</v>
       </c>
     </row>
     <row r="201">
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>34.53078787878784</v>
+        <v>-25.73190303030303</v>
       </c>
       <c r="G201" t="n">
-        <v>0.801590368673328</v>
+        <v>0.9833997567055448</v>
       </c>
     </row>
     <row r="202">
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>19.38050000000001</v>
+        <v>-16.17476545454546</v>
       </c>
       <c r="G202" t="n">
-        <v>0.4900134749369356</v>
+        <v>0.9550594188822812</v>
       </c>
     </row>
     <row r="203">
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>106.8738989898989</v>
+        <v>-44.12183838383836</v>
       </c>
       <c r="G203" t="n">
-        <v>0.6426164623487793</v>
+        <v>0.7671137429896129</v>
       </c>
     </row>
     <row r="204">
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>14.50545454545455</v>
+        <v>-16.73167727272728</v>
       </c>
       <c r="G204" t="n">
-        <v>0.5743203065529865</v>
+        <v>0.9661755760829677</v>
       </c>
     </row>
     <row r="205">
@@ -7191,10 +7191,10 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>94.92404040404035</v>
+        <v>-44.08694949494949</v>
       </c>
       <c r="G205" t="n">
-        <v>0.6232639248252287</v>
+        <v>0.7023318071013005</v>
       </c>
     </row>
     <row r="206">
@@ -7224,10 +7224,10 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>17.77650000000001</v>
+        <v>-15.24843454545456</v>
       </c>
       <c r="G206" t="n">
-        <v>0.4775876675537089</v>
+        <v>0.9398069387444065</v>
       </c>
     </row>
     <row r="207">
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>83.64424242424236</v>
+        <v>-41.22447272727273</v>
       </c>
       <c r="G207" t="n">
-        <v>0.5963832615429521</v>
+        <v>0.7030654986529552</v>
       </c>
     </row>
     <row r="208">
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>13.4680090909091</v>
+        <v>-14.91643818181819</v>
       </c>
       <c r="G208" t="n">
-        <v>0.5568270431952078</v>
+        <v>0.9273076601338307</v>
       </c>
     </row>
     <row r="209">
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>52.02933333333329</v>
+        <v>-36.07471515151512</v>
       </c>
       <c r="G209" t="n">
-        <v>0.5659700583001526</v>
+        <v>0.7257288760139549</v>
       </c>
     </row>
     <row r="210">
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>3.078663636363639</v>
+        <v>-14.09371909090909</v>
       </c>
       <c r="G210" t="n">
-        <v>0.1619249893076498</v>
+        <v>0.9344698728014542</v>
       </c>
     </row>
     <row r="211">
@@ -7389,10 +7389,10 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>6.315365656565653</v>
+        <v>-5.096064646464638</v>
       </c>
       <c r="G211" t="n">
-        <v>0.7629348672404517</v>
+        <v>0.97032222340246</v>
       </c>
     </row>
     <row r="212">
@@ -7422,10 +7422,10 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1.349213636363638</v>
+        <v>-1.828984545454547</v>
       </c>
       <c r="G212" t="n">
-        <v>0.6800541196411853</v>
+        <v>0.8376222861952679</v>
       </c>
     </row>
     <row r="213">
@@ -7455,10 +7455,10 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>9.396715151515149</v>
+        <v>-6.85314747474747</v>
       </c>
       <c r="G213" t="n">
-        <v>0.687468488111328</v>
+        <v>0.6002947681538997</v>
       </c>
     </row>
     <row r="214">
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>2.205565454545455</v>
+        <v>-1.733170909090911</v>
       </c>
       <c r="G214" t="n">
-        <v>0.6980836956826602</v>
+        <v>0.8574505421724945</v>
       </c>
     </row>
     <row r="215">
@@ -7521,10 +7521,10 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>9.251018181818175</v>
+        <v>-6.570703030303026</v>
       </c>
       <c r="G215" t="n">
-        <v>0.7484436638905222</v>
+        <v>0.650689441064757</v>
       </c>
     </row>
     <row r="216">
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>2.957255454545456</v>
+        <v>-2.00335090909091</v>
       </c>
       <c r="G216" t="n">
-        <v>0.7418846888913884</v>
+        <v>0.8653308923231509</v>
       </c>
     </row>
     <row r="217">
@@ -7587,10 +7587,10 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>9.806650505050506</v>
+        <v>-6.673620202020192</v>
       </c>
       <c r="G217" t="n">
-        <v>0.7105121298080754</v>
+        <v>0.5929663775632794</v>
       </c>
     </row>
     <row r="218">
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>1.909564545454547</v>
+        <v>-1.580134545454547</v>
       </c>
       <c r="G218" t="n">
-        <v>0.7342258639372268</v>
+        <v>0.7991625249073988</v>
       </c>
     </row>
     <row r="219">
@@ -7653,10 +7653,10 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>10.00414949494949</v>
+        <v>-5.996492929292924</v>
       </c>
       <c r="G219" t="n">
-        <v>0.7274747066042533</v>
+        <v>0.6275763647414789</v>
       </c>
     </row>
     <row r="220">
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>1.522493636363636</v>
+        <v>-1.717148181818183</v>
       </c>
       <c r="G220" t="n">
-        <v>0.7854877198933863</v>
+        <v>0.8811560208478768</v>
       </c>
     </row>
     <row r="221">
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>14.36420202020202</v>
+        <v>-29.96067878787877</v>
       </c>
       <c r="G221" t="n">
-        <v>0.7820266183555665</v>
+        <v>0.9612104174120865</v>
       </c>
     </row>
     <row r="222">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>5.813172727272732</v>
+        <v>-19.43840454545456</v>
       </c>
       <c r="G222" t="n">
-        <v>0.8512595961380974</v>
+        <v>0.9571051532631568</v>
       </c>
     </row>
     <row r="223">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>24.81296969696967</v>
+        <v>-34.05254545454543</v>
       </c>
       <c r="G223" t="n">
-        <v>0.6218890529314796</v>
+        <v>0.7644517299792474</v>
       </c>
     </row>
     <row r="224">
@@ -7818,10 +7818,10 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>6.529072727272733</v>
+        <v>-17.7260390909091</v>
       </c>
       <c r="G224" t="n">
-        <v>0.8563890226019045</v>
+        <v>0.9722864534755064</v>
       </c>
     </row>
     <row r="225">
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>23.52965656565655</v>
+        <v>-35.66587474747473</v>
       </c>
       <c r="G225" t="n">
-        <v>0.5309557263603214</v>
+        <v>0.7376069779071779</v>
       </c>
     </row>
     <row r="226">
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>6.180209090909092</v>
+        <v>-16.81554272727273</v>
       </c>
       <c r="G226" t="n">
-        <v>0.7989376230654989</v>
+        <v>0.9696587862420163</v>
       </c>
     </row>
     <row r="227">
@@ -7917,10 +7917,10 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>23.18537373737372</v>
+        <v>-31.87787474747473</v>
       </c>
       <c r="G227" t="n">
-        <v>0.5600225338306553</v>
+        <v>0.7459443454220018</v>
       </c>
     </row>
     <row r="228">
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>5.471909090909091</v>
+        <v>-16.80292000000001</v>
       </c>
       <c r="G228" t="n">
-        <v>0.8350132477968052</v>
+        <v>0.9679596641618186</v>
       </c>
     </row>
     <row r="229">
@@ -7983,10 +7983,10 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>22.42032323232323</v>
+        <v>-22.00317575757573</v>
       </c>
       <c r="G229" t="n">
-        <v>0.4978701853338453</v>
+        <v>0.7993891962234576</v>
       </c>
     </row>
     <row r="230">
@@ -8016,10 +8016,10 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>5.119518181818178</v>
+        <v>-17.20258272727274</v>
       </c>
       <c r="G230" t="n">
-        <v>0.954740801080443</v>
+        <v>0.9646629432038121</v>
       </c>
     </row>
     <row r="231">
@@ -8049,10 +8049,10 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>9.120020202020195</v>
+        <v>-2.750004040404039</v>
       </c>
       <c r="G231" t="n">
-        <v>0.8928122084486459</v>
+        <v>0.9388301968630022</v>
       </c>
     </row>
     <row r="232">
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>4.041169090909092</v>
+        <v>-1.581208181818183</v>
       </c>
       <c r="G232" t="n">
-        <v>0.6291295413211266</v>
+        <v>0.8594702420507929</v>
       </c>
     </row>
     <row r="233">
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>29.89160808080806</v>
+        <v>-6.150072727272727</v>
       </c>
       <c r="G233" t="n">
-        <v>0.8111736751570564</v>
+        <v>0.6848843926652464</v>
       </c>
     </row>
     <row r="234">
@@ -8148,10 +8148,10 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>5.646340909090914</v>
+        <v>-1.588303636363637</v>
       </c>
       <c r="G234" t="n">
-        <v>0.6214773292140463</v>
+        <v>0.8882002787386946</v>
       </c>
     </row>
     <row r="235">
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>28.47535757575756</v>
+        <v>-5.713604040404037</v>
       </c>
       <c r="G235" t="n">
-        <v>0.7989219595789877</v>
+        <v>0.7175375423112127</v>
       </c>
     </row>
     <row r="236">
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>5.679169090909093</v>
+        <v>-1.712092727272728</v>
       </c>
       <c r="G236" t="n">
-        <v>0.5814715693173383</v>
+        <v>0.8730903514410934</v>
       </c>
     </row>
     <row r="237">
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>28.806202020202</v>
+        <v>-5.628064646464647</v>
       </c>
       <c r="G237" t="n">
-        <v>0.7797890948786579</v>
+        <v>0.6674042919824781</v>
       </c>
     </row>
     <row r="238">
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>5.576427272727276</v>
+        <v>-1.647535454545455</v>
       </c>
       <c r="G238" t="n">
-        <v>0.595872686247799</v>
+        <v>0.8883969158621721</v>
       </c>
     </row>
     <row r="239">
@@ -8313,10 +8313,10 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>23.53157979797979</v>
+        <v>-5.972412121212118</v>
       </c>
       <c r="G239" t="n">
-        <v>0.6772322309253636</v>
+        <v>0.6731744271831874</v>
       </c>
     </row>
     <row r="240">
@@ -8346,10 +8346,10 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>1.6333</v>
+        <v>-1.644293636363637</v>
       </c>
       <c r="G240" t="n">
-        <v>0.7570581008625206</v>
+        <v>0.8656067014357364</v>
       </c>
     </row>
     <row r="241">
@@ -8379,10 +8379,10 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>3.174933333333328</v>
+        <v>-3.488759595959596</v>
       </c>
       <c r="G241" t="n">
-        <v>0.9036157232740322</v>
+        <v>0.9684892205632327</v>
       </c>
     </row>
     <row r="242">
@@ -8412,10 +8412,10 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>1.925137272727269</v>
+        <v>-2.429803636363638</v>
       </c>
       <c r="G242" t="n">
-        <v>0.7469517746191181</v>
+        <v>0.9259010565878173</v>
       </c>
     </row>
     <row r="243">
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>2.934408080808077</v>
+        <v>-5.844387878787877</v>
       </c>
       <c r="G243" t="n">
-        <v>0.6145635368786302</v>
+        <v>0.6752825468120611</v>
       </c>
     </row>
     <row r="244">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>0.8321336363636374</v>
+        <v>-2.343459090909092</v>
       </c>
       <c r="G244" t="n">
-        <v>0.836189585375508</v>
+        <v>0.9070031224487032</v>
       </c>
     </row>
     <row r="245">
@@ -8511,10 +8511,10 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>5.516989898989894</v>
+        <v>-6.375054545454542</v>
       </c>
       <c r="G245" t="n">
-        <v>0.7174198893736369</v>
+        <v>0.611849162443271</v>
       </c>
     </row>
     <row r="246">
@@ -8544,10 +8544,10 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>1.380197272727274</v>
+        <v>-2.280858181818183</v>
       </c>
       <c r="G246" t="n">
-        <v>0.8308160409427036</v>
+        <v>0.915929888631781</v>
       </c>
     </row>
     <row r="247">
@@ -8577,10 +8577,10 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>6.45862222222222</v>
+        <v>-5.732169696969696</v>
       </c>
       <c r="G247" t="n">
-        <v>0.75892810966105</v>
+        <v>0.6780493355526753</v>
       </c>
     </row>
     <row r="248">
@@ -8610,10 +8610,10 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>1.277790909090911</v>
+        <v>-2.267899090909091</v>
       </c>
       <c r="G248" t="n">
-        <v>0.8296140651120392</v>
+        <v>0.9119184628056705</v>
       </c>
     </row>
     <row r="249">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>7.609931313131313</v>
+        <v>-5.906597979797977</v>
       </c>
       <c r="G249" t="n">
-        <v>0.7118954885081972</v>
+        <v>0.6133496229659199</v>
       </c>
     </row>
     <row r="250">
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>1.146560000000001</v>
+        <v>-2.110050909090908</v>
       </c>
       <c r="G250" t="n">
-        <v>0.8762002233919225</v>
+        <v>0.8978096421670468</v>
       </c>
     </row>
     <row r="251">
@@ -8709,10 +8709,10 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>11.28751515151517</v>
+        <v>-47.23033131313127</v>
       </c>
       <c r="G251" t="n">
-        <v>0.8034227022054671</v>
+        <v>0.9687811453386003</v>
       </c>
     </row>
     <row r="252">
@@ -8742,10 +8742,10 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>6.976772727272737</v>
+        <v>-35.66916818181819</v>
       </c>
       <c r="G252" t="n">
-        <v>0.9481180687531094</v>
+        <v>0.9786228144553953</v>
       </c>
     </row>
     <row r="253">
@@ -8775,10 +8775,10 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>14.39692929292931</v>
+        <v>-56.27193939393936</v>
       </c>
       <c r="G253" t="n">
-        <v>0.7934852275252611</v>
+        <v>0.8462552735884414</v>
       </c>
     </row>
     <row r="254">
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>5.808181818181831</v>
+        <v>-31.87177909090911</v>
       </c>
       <c r="G254" t="n">
-        <v>0.9420809133972532</v>
+        <v>0.9658816180369403</v>
       </c>
     </row>
     <row r="255">
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>16.68395959595959</v>
+        <v>-76.43181414141411</v>
       </c>
       <c r="G255" t="n">
-        <v>0.6665408609350674</v>
+        <v>0.7354775256038646</v>
       </c>
     </row>
     <row r="256">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>7.199145454545455</v>
+        <v>-28.97188727272728</v>
       </c>
       <c r="G256" t="n">
-        <v>0.9635599553197969</v>
+        <v>0.974501339015218</v>
       </c>
     </row>
     <row r="257">
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>12.71975757575754</v>
+        <v>-53.28363232323233</v>
       </c>
       <c r="G257" t="n">
-        <v>0.7664350577785903</v>
+        <v>0.8504701171424065</v>
       </c>
     </row>
     <row r="258">
@@ -8940,10 +8940,10 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>6.34697272727273</v>
+        <v>-32.15614000000002</v>
       </c>
       <c r="G258" t="n">
-        <v>0.9431006724208985</v>
+        <v>0.9756321721492753</v>
       </c>
     </row>
     <row r="259">
@@ -8973,10 +8973,10 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>8.783313131313106</v>
+        <v>-41.48136565656563</v>
       </c>
       <c r="G259" t="n">
-        <v>0.9886816962504369</v>
+        <v>0.9898382506891438</v>
       </c>
     </row>
     <row r="260">
@@ -9006,10 +9006,10 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>6.657127272727269</v>
+        <v>-33.47507181818184</v>
       </c>
       <c r="G260" t="n">
-        <v>0.9815868521947879</v>
+        <v>0.9812346860427383</v>
       </c>
     </row>
   </sheetData>
